--- a/wishlist_videogiochi.xlsx
+++ b/wishlist_videogiochi.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist'!$A$1:$I$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist'!$A$1:$I$94</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -157,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WishlistTable" displayName="WishlistTable" ref="A1:I91" headerRowCount="1">
-  <autoFilter ref="A1:I91"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WishlistTable" displayName="WishlistTable" ref="A1:I94" headerRowCount="1">
+  <autoFilter ref="A1:I94"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Platform"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2221,10 +2221,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Adventure Time</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>2DARK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Limited Edition</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2256,7 +2260,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Castlevania Requiem</t>
+          <t>Adventure Time</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -2267,7 +2271,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2291,14 +2295,10 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Steelbook edition</t>
-        </is>
-      </c>
+          <t>Castlevania Requiem</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2330,10 +2330,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Days gone</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Steelbook edition</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2365,7 +2369,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DETROIT become human</t>
+          <t>Days gone</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2400,7 +2404,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Doom 2016</t>
+          <t>DETROIT become human</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2435,7 +2439,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Doom Eternal</t>
+          <t>Doom 2016</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2470,7 +2474,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dragon Age: Inquisition</t>
+          <t>Doom Eternal</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2505,7 +2509,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dragon Quest XI</t>
+          <t>Dragon Age: Inquisition</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2540,7 +2544,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ecodya</t>
+          <t>Dragon Ball Xenoverse</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2575,7 +2579,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Elden Ring</t>
+          <t>Dragon Quest XI</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2610,7 +2614,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Final Fantasz VII Remake</t>
+          <t>Ecodya</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2645,7 +2649,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fractured but whole</t>
+          <t>Elden Ring</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ghost song</t>
+          <t>Final Fantasz VII Remake</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2715,7 +2719,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gran thefth auto V</t>
+          <t>Fractured but whole</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2750,7 +2754,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gravity rush</t>
+          <t>Ghost song</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2785,7 +2789,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hollow Knight</t>
+          <t>Gran thefth auto V</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2820,7 +2824,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hotline Miami Collection</t>
+          <t>Gravity rush</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2855,7 +2859,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ikai</t>
+          <t>Gravity Rush 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2890,7 +2894,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>It takes two</t>
+          <t>Hollow Knight</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2925,7 +2929,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Katamari Damacy Reroll</t>
+          <t>Hotline Miami Collection</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2960,7 +2964,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Little nightmares II</t>
+          <t>Ikai</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2995,7 +2999,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Little nightmares III</t>
+          <t>Inside/Limbo</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -3030,14 +3034,10 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Made in Abyss</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Cartonata</t>
-        </is>
-      </c>
+          <t>It takes two</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mafia trilogy</t>
+          <t>Katamari Damacy Reroll</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Marvel's Spiderman</t>
+          <t>Little nightmares III</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3139,10 +3139,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metal Gear Solid: The phantom pain</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Made in Abyss</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Cartonata</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3174,14 +3178,10 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Monster Hunter: World</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Cartonata</t>
-        </is>
-      </c>
+          <t>Mafia trilogy</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nier replicant</t>
+          <t>Marvel's Spiderman</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nioh 2</t>
+          <t>Metal Gear Solid: The phantom pain</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3283,10 +3283,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No man's sky</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Monster Hunter: World</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Cartonata</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3318,7 +3322,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Okami HD</t>
+          <t>Nier replicant</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3353,7 +3357,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Outer wilds</t>
+          <t>Nioh 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3388,7 +3392,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Persona 5</t>
+          <t>No man's sky</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -3423,7 +3427,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Psychonauts</t>
+          <t>Okami HD</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3458,7 +3462,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Psychonauts 2</t>
+          <t>Outer wilds</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -3469,7 +3473,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3493,7 +3497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sekiro Shadows Die Twice</t>
+          <t>Persona 5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -3528,14 +3532,10 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Song of Horror</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Deluxe edition</t>
-        </is>
-      </c>
+          <t>Psychonauts</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3567,14 +3567,10 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sonic Mania</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Cartonata</t>
-        </is>
-      </c>
+          <t>Psychonauts 2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3606,14 +3602,10 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stray</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Cartoline</t>
-        </is>
-      </c>
+          <t>Resident Evil Origins Collection</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3645,7 +3637,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>The Binding of Isaac: Afterbirth</t>
+          <t>Scribblenauts</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -3656,7 +3648,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3680,7 +3672,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>The Last of Us part II</t>
+          <t>Sekiro Shadows Die Twice</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3702,9 +3694,118 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>W0091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PS4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Song of Horror</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Deluxe edition</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>W0092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PS4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>The Binding of Isaac: Afterbirth</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>W0093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PS4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>The Last of Us part II</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I91"/>
-  <conditionalFormatting sqref="A2:I91">
+  <autoFilter ref="A1:I94"/>
+  <conditionalFormatting sqref="A2:I94">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>=$F2="Yes"</formula>
     </cfRule>
@@ -3713,13 +3814,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="B2:B91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PS1,PS2,PS4,DS WII"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:G91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:G94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
   </dataValidations>

--- a/wishlist_videogiochi.xlsx
+++ b/wishlist_videogiochi.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist'!$A$1:$I$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist'!$A$1:$I$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -157,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WishlistTable" displayName="WishlistTable" ref="A1:I94" headerRowCount="1">
-  <autoFilter ref="A1:I94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WishlistTable" displayName="WishlistTable" ref="A1:I79" headerRowCount="1">
+  <autoFilter ref="A1:I79"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Platform"/>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ape Escape 3</t>
+          <t>Blood Will Tell</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Blood Will Tell</t>
+          <t>Dark Chronicle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -992,7 +992,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Castlevania</t>
+          <t>Forbidden Siren 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dark Chronicle</t>
+          <t>Futurama</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1062,10 +1062,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dark Cloud</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>GTA Trilogy</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Versione cartonata</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1097,7 +1101,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Forbidden Siren 2</t>
+          <t>Half Life</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Futurama</t>
+          <t>Haunting Ground</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1167,14 +1171,10 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GTA Trilogy</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Versione cartonata</t>
-        </is>
-      </c>
+          <t>Jak 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Half Life</t>
+          <t>Jak 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Haunting Ground</t>
+          <t>Killer7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jak 2</t>
+          <t>Kingdom Hearts 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jak 3</t>
+          <t>Le avventure di Lupin III: Lupin la morte Zenigata l'amore</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Killer7</t>
+          <t>Lemmings</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kingdom Hearts 2</t>
+          <t>Manhunt</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Le avventure di Lupin III: Lupin la morte Zenigata l'amore</t>
+          <t>Manhunt 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lemmings</t>
+          <t>Maximo</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Manhunt</t>
+          <t>Monster Hunter</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Manhunt 2</t>
+          <t>Nightmare Before Christmas Oogie's Revenge</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Maximo</t>
+          <t>Onimusha</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monster Hunter</t>
+          <t>Onimusha II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nightmare Before Christmas Oogie's Revenge</t>
+          <t>Onimusha III</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Onimusha</t>
+          <t>Project Zero II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Onimusha II</t>
+          <t>Project Zero III</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Onimusha III</t>
+          <t>Ratchet &amp; Clank: l'altezza non conta</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Project Zero II</t>
+          <t>Secret Agent Clank</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Project Zero III</t>
+          <t>Silent Hill 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ratchet &amp; Clank: l'altezza non conta</t>
+          <t>Silent Hill 4 The Room</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Secret Agent Clank</t>
+          <t>Silent Hill: Shattered Memories</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Silent Hill 2</t>
+          <t>Splatter master</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Silent Hill 4 The Room</t>
+          <t>Syberia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Silent Hill: Shattered Memories</t>
+          <t>Syberia II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Splatter master</t>
+          <t>Yakuza</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Syberia</t>
+          <t>Yakuza 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PS2</t>
+          <t>PS4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Syberia II</t>
+          <t>.hack//GU Last Recode</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2111,15 +2111,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PS2</t>
+          <t>PS4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yakuza</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>2DARK</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Limited Edition</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2146,12 +2150,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PS2</t>
+          <t>PS4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yakuza 2</t>
+          <t>Castlevania Requiem</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2186,10 +2190,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>.hack//GU Last Recode</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Steelbook edition</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2221,14 +2229,10 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2DARK</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Limited Edition</t>
-        </is>
-      </c>
+          <t>Days gone</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2260,7 +2264,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Adventure Time</t>
+          <t>Doom 2016</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -2271,7 +2275,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2295,7 +2299,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Castlevania Requiem</t>
+          <t>Doom Eternal</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2330,14 +2334,10 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Steelbook edition</t>
-        </is>
-      </c>
+          <t>Dragon Age: Inquisition</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Days gone</t>
+          <t>Dragon Ball Xenoverse</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DETROIT become human</t>
+          <t>Ecodya</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Doom 2016</t>
+          <t>Elden Ring</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Doom Eternal</t>
+          <t>Final Fantasy VII Remake</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dragon Age: Inquisition</t>
+          <t>Fractured but whole</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dragon Ball Xenoverse</t>
+          <t>Ghost song</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dragon Quest XI</t>
+          <t>Gran thefth auto V</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ecodya</t>
+          <t>Gravity Rush 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Elden Ring</t>
+          <t>Hotline Miami Collection</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Final Fantasz VII Remake</t>
+          <t>Ikai</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fractured but whole</t>
+          <t>Inside/Limbo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ghost song</t>
+          <t>Katamari Damacy Reroll</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gran thefth auto V</t>
+          <t>Kingdom Majestic</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2824,10 +2824,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gravity rush</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Made in Abyss</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Cartonata</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2835,7 +2839,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2859,7 +2863,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gravity Rush 2</t>
+          <t>Marvel's Spiderman</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2894,7 +2898,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hollow Knight</t>
+          <t>Metal Gear Solid: The phantom pain</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2929,10 +2933,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hotline Miami Collection</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Monster Hunter: World</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Cartonata</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -2964,7 +2972,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ikai</t>
+          <t>Nioh 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2999,7 +3007,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Inside/Limbo</t>
+          <t>No man's sky</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -3034,7 +3042,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>It takes two</t>
+          <t>Psychonauts</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -3069,7 +3077,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Katamari Damacy Reroll</t>
+          <t>Psychonauts 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -3104,7 +3112,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Little nightmares III</t>
+          <t>Remothered: Tormented Fathers</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3139,14 +3147,10 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Made in Abyss</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Cartonata</t>
-        </is>
-      </c>
+          <t>Resident Evil Origins Collection</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3178,7 +3182,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mafia trilogy</t>
+          <t>Sekiro Shadows Die Twice</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3213,10 +3217,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Marvel's Spiderman</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Song of Horror</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Deluxe edition</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>Medium</t>
@@ -3248,7 +3256,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Metal Gear Solid: The phantom pain</t>
+          <t>Super Meat Boy</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3270,542 +3278,9 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>W0079</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Monster Hunter: World</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Cartonata</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>W0080</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Nier replicant</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>W0081</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Nioh 2</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>W0082</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>No man's sky</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>W0083</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Okami HD</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>W0084</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Outer wilds</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>W0085</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Persona 5</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>W0086</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Psychonauts</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>W0087</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Psychonauts 2</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>W0088</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Resident Evil Origins Collection</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>W0089</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Scribblenauts</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>W0090</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Sekiro Shadows Die Twice</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>W0091</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Song of Horror</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Deluxe edition</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>W0092</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>The Binding of Isaac: Afterbirth</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>W0093</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>PS4</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>The Last of Us part II</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I94"/>
-  <conditionalFormatting sqref="A2:I94">
+  <autoFilter ref="A1:I79"/>
+  <conditionalFormatting sqref="A2:I79">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>=$F2="Yes"</formula>
     </cfRule>
@@ -3814,13 +3289,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="B2:B94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PS1,PS2,PS4,DS WII"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:G94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:G79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E94" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
   </dataValidations>

--- a/wishlist_videogiochi.xlsx
+++ b/wishlist_videogiochi.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist'!$A$1:$I$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wishlist'!$A$1:$L$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -157,18 +157,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WishlistTable" displayName="WishlistTable" ref="A1:I79" headerRowCount="1">
-  <autoFilter ref="A1:I79"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WishlistTable" displayName="WishlistTable" ref="A1:L79" headerRowCount="1">
+  <autoFilter ref="A1:L79"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Platform"/>
     <tableColumn id="3" name="Title"/>
     <tableColumn id="4" name="Note"/>
     <tableColumn id="5" name="Priority"/>
-    <tableColumn id="6" name="In Transit"/>
-    <tableColumn id="7" name="Received"/>
-    <tableColumn id="8" name="Ordered Date"/>
-    <tableColumn id="9" name="Received Date"/>
+    <tableColumn id="6" name="Target Price"/>
+    <tableColumn id="7" name="In Transit"/>
+    <tableColumn id="8" name="Received"/>
+    <tableColumn id="9" name="Ordered Date"/>
+    <tableColumn id="10" name="Received Date"/>
+    <tableColumn id="11" name="Listing URL"/>
+    <tableColumn id="12" name="Replacement"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,10 +474,13 @@
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,22 +511,37 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Target Price</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>In Transit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ordered Date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Received Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Listing URL</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Replacement</t>
         </is>
       </c>
     </row>
@@ -546,18 +567,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,18 +609,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -616,18 +651,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -651,18 +693,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -686,18 +735,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -721,18 +777,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -756,18 +819,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -791,18 +861,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -826,18 +903,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -861,18 +945,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -896,18 +987,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -931,18 +1029,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -966,18 +1071,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1001,18 +1113,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1036,18 +1155,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1075,18 +1201,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1110,18 +1243,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1145,18 +1285,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1180,18 +1327,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1215,18 +1369,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1250,18 +1411,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1285,18 +1453,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1320,18 +1495,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1355,18 +1537,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1390,18 +1579,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1425,18 +1621,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1460,18 +1663,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1495,18 +1705,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1530,18 +1747,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1565,18 +1789,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1600,18 +1831,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1635,18 +1873,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1670,18 +1915,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1705,18 +1957,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1740,18 +1999,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1775,18 +2041,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1810,18 +2083,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1845,18 +2125,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1880,18 +2167,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1915,18 +2209,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1950,18 +2251,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1985,18 +2293,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2020,18 +2335,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2055,18 +2377,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2090,18 +2419,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2129,18 +2465,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2164,18 +2507,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2203,18 +2553,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2238,18 +2595,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2273,18 +2637,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2308,18 +2679,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2343,18 +2721,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2378,18 +2763,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2413,18 +2805,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2448,18 +2847,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2483,18 +2889,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2518,18 +2931,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2553,18 +2973,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2588,18 +3015,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2623,18 +3057,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2658,18 +3099,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2693,18 +3141,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2728,18 +3183,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2763,18 +3225,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2798,18 +3267,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2837,18 +3313,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2872,18 +3355,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2907,18 +3397,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2946,18 +3443,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2981,18 +3485,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3016,18 +3527,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3051,18 +3569,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3086,18 +3611,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3121,18 +3653,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3156,18 +3695,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3191,18 +3737,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3230,18 +3783,25 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3265,34 +3825,41 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I79"/>
-  <conditionalFormatting sqref="A2:I79">
+  <autoFilter ref="A1:L79"/>
+  <conditionalFormatting sqref="A2:L79">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
-      <formula>=$F2="Yes"</formula>
+      <formula>=$G2="Yes"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="0">
-      <formula>=$G2="Yes"</formula>
+      <formula>=$H2="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="B2:B79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PS1,PS2,PS4,DS WII"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:G79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:H79 L2:L79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -3338,7 +3905,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIFS(Wishlist!G:G,"No")</f>
+        <f>COUNTIFS(Wishlist!H:H,"No")</f>
         <v/>
       </c>
     </row>
@@ -3349,7 +3916,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIFS(Wishlist!F:F,"Yes",Wishlist!G:G,"No")</f>
+        <f>COUNTIFS(Wishlist!G:G,"Yes",Wishlist!H:H,"No")</f>
         <v/>
       </c>
     </row>
@@ -3360,7 +3927,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIFS(Wishlist!G:G,"Yes")</f>
+        <f>COUNTIFS(Wishlist!H:H,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -3371,7 +3938,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIFS(Wishlist!B:B,"PS1",Wishlist!G:G,"No")</f>
+        <f>COUNTIFS(Wishlist!B:B,"PS1",Wishlist!H:H,"No")</f>
         <v/>
       </c>
     </row>
@@ -3382,7 +3949,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIFS(Wishlist!B:B,"PS2",Wishlist!G:G,"No")</f>
+        <f>COUNTIFS(Wishlist!B:B,"PS2",Wishlist!H:H,"No")</f>
         <v/>
       </c>
     </row>
@@ -3393,7 +3960,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIFS(Wishlist!B:B,"PS4",Wishlist!G:G,"No")</f>
+        <f>COUNTIFS(Wishlist!B:B,"PS4",Wishlist!H:H,"No")</f>
         <v/>
       </c>
     </row>
@@ -3404,7 +3971,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIFS(Wishlist!B:B,"DS WII",Wishlist!G:G,"No")</f>
+        <f>COUNTIFS(Wishlist!B:B,"DS WII",Wishlist!H:H,"No")</f>
         <v/>
       </c>
     </row>
